--- a/Decrypt/template.xlsx
+++ b/Decrypt/template.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\Decrypt\Decrypt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1F56F6-957C-46CC-A688-385AB0FC3CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C735D676-2F99-4615-9AA6-DEC0AAD8678C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{6FD89727-CC28-47F9-BFF3-FE49F336E56B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{6FD89727-CC28-47F9-BFF3-FE49F336E56B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tests">Sheet1!$B$5:$G$6</definedName>
+    <definedName name="Tests">Sheet1!$B$5:$K$6</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>产品编码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -115,6 +115,38 @@
   </si>
   <si>
     <t>{{item.XMax_Y}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X最小力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X最大力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y最小力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y最大力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{item.XDirMin}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{item.XDirMax}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{item.YDirMin}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{item.YDirMax}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -495,14 +527,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D403971-4FCE-4628-94E1-071DA5821ABE}">
-  <dimension ref="B1:G5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:K5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="15.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,7 +551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -536,7 +568,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
@@ -553,10 +585,22 @@
         <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -573,6 +617,18 @@
         <v>20</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>17</v>
       </c>
     </row>

--- a/Decrypt/template.xlsx
+++ b/Decrypt/template.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\Decrypt\Decrypt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rensh\source\repos\renshujian\Decrypt\Decrypt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C735D676-2F99-4615-9AA6-DEC0AAD8678C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CD624A-6E77-4371-972D-025235579377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{6FD89727-CC28-47F9-BFF3-FE49F336E56B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{6FD89727-CC28-47F9-BFF3-FE49F336E56B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tests">Sheet1!$B$5:$K$6</definedName>
+    <definedName name="Tests">Sheet1!$B$5:$L$6</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,28 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>产品编码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>起始浮动力下限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>起始浮动力上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大浮动力下限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大浮动力上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>位置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -78,22 +62,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{{InitialLowerLimit}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{InitialUpperLimit}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{FinalLowerLimit}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{FinalUpperLimit}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{{item.Index}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,6 +115,78 @@
   </si>
   <si>
     <t>{{item.YDirMax}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起始浮动力下限1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起始浮动力上限1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大浮动力下限1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大浮动力上限1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起始浮动力下限2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起始浮动力上限2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大浮动力下限2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大浮动力上限2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{InitialLowerLimit1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{InitialUpperLimit1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{FinalLowerLimit1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{FinalUpperLimit1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{InitialLowerLimit2}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{InitialUpperLimit2}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{FinalLowerLimit2}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{FinalUpperLimit2}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上下限参数组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{item.LimitGroup}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -527,109 +567,141 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D403971-4FCE-4628-94E1-071DA5821ABE}">
-  <dimension ref="B1:K5"/>
+  <dimension ref="B1:L5"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.9296875" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="15.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="15.73046875" customWidth="1"/>
+    <col min="11" max="11" width="12.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
